--- a/results/LCA/lci_comparison_ab/cobalt_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/cobalt_LCIA-results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t>index</t>
   </si>
@@ -43,22 +43,34 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Ecosystem quality | Total ecosystem quality</t>
   </si>
   <si>
-    <t>cobalt hydroxide | cobalt hydroxide, via hydrometallurigcal ore procesing, economic allocation | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>cobalt | cobalt metal production, from copper mining, via electrolysis, economic allocation | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>cobalt | market for cobalt | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>copper-cobalt ore | market for copper-cobalt ore | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>copper-cobalt ore | copper-cobalt mining, industrial, economic allocation | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>cobalt hydroxide | market for cobalt hydroxide | World | kilogram | premise_generated_db_2025_L</t>
+    <t>cobalt hydroxide | cobalt hydroxide, via hydrometallurigcal ore procesing, economic allocation | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cobalt sulfate | cobalt sulfate production, from copper mining, economic allocation | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>co commodities | cobalt (Co) global market | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cobalt | cobalt metal production, from copper mining, via electrolysis, economic allocation | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper-cobalt ore | copper-cobalt mining, industrial, economic allocation | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cobalt sulfate | market for cobalt sulfate | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cobalt hydroxide | market for cobalt hydroxide | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>copper-cobalt ore | market for copper-cobalt ore | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>co content | cobalt (Co) global market (Co content) | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>cobalt | market for cobalt | World | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>kilogram</t>
@@ -67,37 +79,61 @@
     <t>cobalt hydroxide</t>
   </si>
   <si>
+    <t>cobalt sulfate</t>
+  </si>
+  <si>
+    <t>co commodities</t>
+  </si>
+  <si>
     <t>cobalt</t>
   </si>
   <si>
     <t>copper-cobalt ore</t>
   </si>
   <si>
+    <t>co content</t>
+  </si>
+  <si>
     <t>cobalt hydroxide, via hydrometallurigcal ore procesing, economic allocation</t>
   </si>
   <si>
+    <t>cobalt sulfate production, from copper mining, economic allocation</t>
+  </si>
+  <si>
+    <t>cobalt (Co) global market</t>
+  </si>
+  <si>
     <t>cobalt metal production, from copper mining, via electrolysis, economic allocation</t>
   </si>
   <si>
+    <t>copper-cobalt mining, industrial, economic allocation</t>
+  </si>
+  <si>
+    <t>market for cobalt sulfate</t>
+  </si>
+  <si>
+    <t>market for cobalt hydroxide</t>
+  </si>
+  <si>
+    <t>market for copper-cobalt ore</t>
+  </si>
+  <si>
+    <t>cobalt (Co) global market (Co content)</t>
+  </si>
+  <si>
     <t>market for cobalt</t>
   </si>
   <si>
-    <t>market for copper-cobalt ore</t>
-  </si>
-  <si>
-    <t>copper-cobalt mining, industrial, economic allocation</t>
-  </si>
-  <si>
-    <t>market for cobalt hydroxide</t>
-  </si>
-  <si>
     <t>CA</t>
   </si>
   <si>
+    <t>GLO</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>premise_generated_db_2025_L</t>
+    <t>premise_db_2025_L</t>
   </si>
 </sst>
 </file>
@@ -455,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -498,25 +534,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>5.10195922869597E-05</v>
+        <v>4.945505032798454E-05</v>
       </c>
       <c r="J2">
-        <v>4.586725953289601</v>
+        <v>4.474272621303089</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -530,25 +566,25 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I3">
-        <v>0.0002839956019121759</v>
+        <v>0.0001053777612014832</v>
       </c>
       <c r="J3">
-        <v>26.74400923711018</v>
+        <v>10.32742373265847</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -562,25 +598,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I4">
-        <v>0.0003026153242946689</v>
+        <v>0.0003864511979138956</v>
       </c>
       <c r="J4">
-        <v>29.12118071362599</v>
+        <v>35.45521355084559</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -594,25 +630,25 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>1.217362848678454E-06</v>
+        <v>0.0002888645297650591</v>
       </c>
       <c r="J5">
-        <v>0.1442483944070043</v>
+        <v>28.4126276453643</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -626,25 +662,25 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>4.224973459237631E-07</v>
+        <v>4.212692773039955E-07</v>
       </c>
       <c r="J6">
-        <v>0.03118286230190171</v>
+        <v>0.03148109786402058</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -658,25 +694,153 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>0.0001066689324007565</v>
+      </c>
+      <c r="J7">
+        <v>10.47891080130374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>5.013906663268171E-05</v>
+      </c>
+      <c r="J8">
+        <v>4.554955812402911</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="s">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7">
-        <v>5.211249017026863E-05</v>
-      </c>
-      <c r="J7">
-        <v>4.722384055364174</v>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9">
+        <v>8.085863383037572E-07</v>
+      </c>
+      <c r="J9">
+        <v>0.08584066746986627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>0.0004858656685109507</v>
+      </c>
+      <c r="J10">
+        <v>44.90515814706148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11">
+        <v>0.0002912885830570907</v>
+      </c>
+      <c r="J11">
+        <v>28.64861388014702</v>
       </c>
     </row>
   </sheetData>

--- a/results/LCA/lci_comparison_ab/cobalt_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/cobalt_LCIA-results.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/lci_comparison_ab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_14BD61F5F613C8264F2C4CD225731F39550AB6C9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7589ABB1-1F93-4EA3-BCB6-C4CF38CD6214}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -139,8 +148,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,12 +166,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -192,24 +213,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -247,7 +278,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -281,6 +312,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -315,9 +347,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,11 +523,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="120.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="75.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -539,23 +584,23 @@
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2">
-        <v>4.945505032798454E-05</v>
-      </c>
-      <c r="J2">
+        <v>4.9455050327984537E-5</v>
+      </c>
+      <c r="J2" s="2">
         <v>4.474272621303089</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -571,28 +616,28 @@
       <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
       </c>
       <c r="I3">
-        <v>0.0001053777612014832</v>
-      </c>
-      <c r="J3">
+        <v>1.053777612014832E-4</v>
+      </c>
+      <c r="J3" s="2">
         <v>10.32742373265847</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -601,30 +646,30 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
         <v>39</v>
       </c>
       <c r="I4">
-        <v>0.0003864511979138956</v>
+        <v>2.8886452976505908E-4</v>
       </c>
       <c r="J4">
-        <v>35.45521355084559</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>28.412627645364299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -633,10 +678,10 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
         <v>36</v>
@@ -645,18 +690,18 @@
         <v>39</v>
       </c>
       <c r="I5">
-        <v>0.0002888645297650591</v>
+        <v>4.212692773039955E-7</v>
       </c>
       <c r="J5">
-        <v>28.4126276453643</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>3.1481097864020577E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -665,153 +710,153 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3.8645119791389562E-4</v>
+      </c>
+      <c r="J6" s="3">
+        <v>35.455213550845592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>4.8586566851095068E-4</v>
+      </c>
+      <c r="J7">
+        <v>44.905158147061478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>1.066689324007565E-4</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10.478910801303741</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9">
+        <v>5.0139066632681708E-5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4.5549558124029108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6">
-        <v>4.212692773039955E-07</v>
-      </c>
-      <c r="J6">
-        <v>0.03148109786402058</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
         <v>38</v>
       </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>0.0001066689324007565</v>
-      </c>
-      <c r="J7">
-        <v>10.47891080130374</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8">
-        <v>5.013906663268171E-05</v>
-      </c>
-      <c r="J8">
-        <v>4.554955812402911</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9">
-        <v>8.085863383037572E-07</v>
-      </c>
-      <c r="J9">
-        <v>0.08584066746986627</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
       <c r="H10" t="s">
         <v>39</v>
       </c>
       <c r="I10">
-        <v>0.0004858656685109507</v>
+        <v>8.0858633830375721E-7</v>
       </c>
       <c r="J10">
-        <v>44.90515814706148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>8.5840667469866266E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -837,13 +882,18 @@
         <v>39</v>
       </c>
       <c r="I11">
-        <v>0.0002912885830570907</v>
+        <v>2.9128858305709068E-4</v>
       </c>
       <c r="J11">
-        <v>28.64861388014702</v>
+        <v>28.648613880147021</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J11">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>